--- a/data/trans_camb/P1429-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1429-Clase-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,09</t>
+          <t>-2,1; 0,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,48</t>
+          <t>-1,78; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,7</t>
+          <t>-1,47; 0,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,84</t>
+          <t>-4,26; 0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,18</t>
+          <t>-3,88; 1,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,6</t>
+          <t>-3,27; 1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,22</t>
+          <t>-2,21; 0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,54</t>
+          <t>-1,84; 0,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,92</t>
+          <t>-1,5; 0,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,33%</t>
+          <t>-26,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,79%</t>
+          <t>-17,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-9,97%</t>
+          <t>-11,7%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 343,26</t>
+          <t>-84,74; 268,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 65,08</t>
+          <t>-87,16; 51,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 59,58</t>
+          <t>-80,61; 54,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 80,36</t>
+          <t>-60,2; 84,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,29; 30,98</t>
+          <t>-85,84; 29,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,93; 49,61</t>
+          <t>-71,4; 60,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,8; 80,67</t>
+          <t>-53,63; 75,23</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; -0,22</t>
+          <t>-2,07; -0,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; -0,22</t>
+          <t>-1,96; -0,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,81; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,08</t>
+          <t>-2,95; 0,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,38</t>
+          <t>-2,63; 1,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,98</t>
+          <t>-1,05; 2,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,12</t>
+          <t>-2,0; 0,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,51</t>
+          <t>-1,88; 0,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,14</t>
+          <t>-1,06; 1,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-82,92%</t>
+          <t>-81,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,95; 108,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 204,73</t>
+          <t>-85,49; 205,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 305,46</t>
+          <t>-35,37; 295,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,56; 39,56</t>
+          <t>-92,82; 22,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,06; 111,24</t>
+          <t>-90,99; 72,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 153,04</t>
+          <t>-50,41; 136,9</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,55</t>
+          <t>-1,79; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,79</t>
+          <t>-1,53; 0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,85</t>
+          <t>-1,19; 1,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 1,61</t>
+          <t>-6,26; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,36</t>
+          <t>-3,84; 6,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 9,28</t>
+          <t>-0,93; 9,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,44</t>
+          <t>-2,29; 0,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,6</t>
+          <t>-1,45; 1,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,02</t>
+          <t>-0,37; 3,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-25,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 328,51</t>
+          <t>-100,0; 272,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,19; 210,88</t>
+          <t>-80,44; 357,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 109,61</t>
+          <t>-85,24; 80,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 283,26</t>
+          <t>-64,13; 302,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 371,29</t>
+          <t>-26,86; 400,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,92; 65,27</t>
+          <t>-83,46; 57,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 152,04</t>
+          <t>-59,37; 148,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,5; 163,5</t>
+          <t>-20,92; 282,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; -0,63</t>
+          <t>-2,01; -0,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,56</t>
+          <t>-2,06; -0,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,46</t>
+          <t>-0,86; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,33</t>
+          <t>-3,38; -0,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,21</t>
+          <t>-3,2; 0,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,74</t>
+          <t>-1,99; 1,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,69</t>
+          <t>-2,12; -0,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; -0,36</t>
+          <t>-1,95; -0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,88</t>
+          <t>-0,81; 0,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,24%</t>
+          <t>-5,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,08%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -48,0</t>
+          <t>-100,0; -47,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,97</t>
+          <t>-100,0; -48,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,65; 151,5</t>
+          <t>-51,29; 129,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-77,37; -7,85</t>
+          <t>-77,56; -8,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 13,59</t>
+          <t>-70,11; 11,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 29,02</t>
+          <t>-42,83; 51,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,02; -37,08</t>
+          <t>-82,19; -36,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,31; -21,25</t>
+          <t>-74,91; -23,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 51,14</t>
+          <t>-31,35; 57,78</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,08</t>
+          <t>-2,59; -0,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,69</t>
+          <t>-1,97; 0,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,36</t>
+          <t>-2,21; 0,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,12</t>
+          <t>-0,38; 4,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,2</t>
+          <t>-2,83; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,16</t>
+          <t>0,26; 4,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,23</t>
+          <t>-0,97; 2,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,47</t>
+          <t>-2,31; 0,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,22</t>
+          <t>-0,25; 2,35</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-57,8%</t>
+          <t>-60,27%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -1652,49 +1652,49 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,22; 228,95</t>
+          <t>-89,4; 288,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-96,35; 129,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 169,22</t>
+          <t>-11,09; 168,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 48,47</t>
+          <t>-58,73; 54,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 162,49</t>
+          <t>4,99; 173,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 107,56</t>
+          <t>-28,55; 98,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 27,99</t>
+          <t>-61,59; 18,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 117,04</t>
+          <t>-5,5; 127,0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,63</t>
+          <t>-1,58; 2,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,57</t>
+          <t>-2,34; 1,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,19</t>
+          <t>-1,63; 2,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,04</t>
+          <t>-1,21; 2,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,21</t>
+          <t>-2,0; 1,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,37</t>
+          <t>-1,44; 1,57</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,08%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 52,65</t>
+          <t>-23,65; 52,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 31,22</t>
+          <t>-34,18; 33,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 44,95</t>
+          <t>-24,81; 40,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 51,01</t>
+          <t>-21,99; 51,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 30,78</t>
+          <t>-37,28; 35,11</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 35,19</t>
+          <t>-26,78; 37,09</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; -0,46</t>
+          <t>-1,2; -0,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; -0,26</t>
+          <t>-1,1; -0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,32</t>
+          <t>-0,64; 0,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,65</t>
+          <t>-1,29; 0,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,04</t>
+          <t>-1,84; 0,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,02</t>
+          <t>-0,4; 1,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; -0,03</t>
+          <t>-1,07; -0,02</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,23</t>
+          <t>-1,32; -0,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,47</t>
+          <t>-0,36; 0,69</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-20,73%</t>
+          <t>-19,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1,15%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-94,22; -47,57</t>
+          <t>-94,11; -54,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-82,8; -32,48</t>
+          <t>-83,84; -37,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,9; 41,28</t>
+          <t>-52,63; 38,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 16,99</t>
+          <t>-26,89; 17,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 1,42</t>
+          <t>-37,74; 2,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 26,43</t>
+          <t>-9,0; 34,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-37,57; -1,41</t>
+          <t>-37,19; -0,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,65; -9,39</t>
+          <t>-44,68; -11,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 19,7</t>
+          <t>-12,04; 29,31</t>
         </is>
       </c>
     </row>
